--- a/docs/thesis/dedup_STRESS_200_v1-verified.xlsx
+++ b/docs/thesis/dedup_STRESS_200_v1-verified.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E1F999-B91B-4216-A66C-7C02333CBE1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
